--- a/TDD_examples/CASE_1_ITER_like_LTS/conductor_1_input.xlsx
+++ b/TDD_examples/CASE_1_ITER_like_LTS/conductor_1_input.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CHAN" sheetId="2" r:id="R559dedfd5cef4e7f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="STACK" sheetId="5" r:id="R8dedf6834b204250"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="STR_MIX" sheetId="3" r:id="R560b6322827a48dc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="STR_STAB" sheetId="6" r:id="R3439971776074c76"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Z_JACKET" sheetId="4" r:id="R38bb5313b1a44a68"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CHAN" sheetId="2" r:id="Rc19db0f5c9664ee8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="STACK" sheetId="5" r:id="R38500839881747de"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="STR_MIX" sheetId="3" r:id="R2ec4b4de27194402"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="STR_STAB" sheetId="6" r:id="R8573d009f09646b4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Z_JACKET" sheetId="4" r:id="R7a8ba3df93934514"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -38,15 +38,9 @@
     <x:t xml:space="preserve">m</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">x coordinate of the barycenter. Not used if flag ITYMESH = -1 in file conductor_grid.</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">Y_barycenter</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">y coordinate of the barycenter. Not used if flag ITYMESH = -1 in file conductor_grid.</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">FLUID_TYPE</x:t>
   </x:si>
   <x:si>
@@ -83,9 +77,6 @@
     <x:t xml:space="preserve">VOID_FRACTION</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">VIOD FRACTION OF THE CHANNEL = VOID AREA/TOTALAREA OF THE CHANNEL</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">IFRICTION</x:t>
   </x:si>
   <x:si>
@@ -144,9 +135,6 @@
   </x:si>
   <x:si>
     <x:t xml:space="preserve">element of the type "SC+Cu strands"</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">row used to get the correct number of mixed copper-supeconductor strands objects in cell B1 as the sum of values in this row starting from cell D2</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">element of the type "Cu strands"</x:t>
@@ -812,8 +800,8 @@
       <x:c r="C5" s="44" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="D5" s="48" t="s">
-        <x:v>8</x:v>
+      <x:c r="D5" s="48" t="str">
+        <x:v>x coordinate of the barycenter. Not used if flag ITYMSH = -1 in file conductor_grid.</x:v>
       </x:c>
       <x:c r="E5" s="45">
         <x:v>0</x:v>
@@ -824,7 +812,7 @@
     </x:row>
     <x:row r="6" ht="15" hidden="0" customHeight="1">
       <x:c r="A6" s="43" t="s">
-        <x:v>9</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B6" s="44" t="s">
         <x:v>7</x:v>
@@ -832,8 +820,8 @@
       <x:c r="C6" s="44" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="D6" s="48" t="s">
-        <x:v>10</x:v>
+      <x:c r="D6" s="48" t="str">
+        <x:v>y coordinate of the barycenter. Not used if flag ITYMSH = -1 in file conductor_grid.</x:v>
       </x:c>
       <x:c r="E6" s="45">
         <x:v>0</x:v>
@@ -844,27 +832,27 @@
     </x:row>
     <x:row r="7" ht="15" hidden="0" customHeight="1">
       <x:c r="A7" s="43" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="B7" s="44" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="C7" s="44" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="B7" s="44" t="s">
+      <x:c r="D7" s="48" t="s">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="C7" s="44" t="s">
+      <x:c r="E7" s="44" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="D7" s="48" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="E7" s="44" t="s">
-        <x:v>15</x:v>
-      </x:c>
       <x:c r="F7" s="44" t="s">
-        <x:v>15</x:v>
+        <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="15" hidden="0" customHeight="1">
       <x:c r="A8" s="43" t="s">
-        <x:v>16</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B8" s="44" t="s">
         <x:v>7</x:v>
@@ -873,7 +861,7 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="D8" s="48" t="s">
-        <x:v>17</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E8" s="46">
         <x:v>8.0000000000000002E-3</x:v>
@@ -884,7 +872,7 @@
     </x:row>
     <x:row r="9" ht="15" hidden="0" customHeight="1">
       <x:c r="A9" s="43" t="s">
-        <x:v>18</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B9" s="44" t="s">
         <x:v>7</x:v>
@@ -893,7 +881,7 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="D9" s="48" t="s">
-        <x:v>19</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="E9" s="46">
         <x:v>0</x:v>
@@ -904,16 +892,16 @@
     </x:row>
     <x:row r="10" ht="15" hidden="0" customHeight="1">
       <x:c r="A10" s="43" t="s">
-        <x:v>20</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B10" s="44" t="s">
-        <x:v>12</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C10" s="44" t="s">
         <x:v>4</x:v>
       </x:c>
       <x:c r="D10" s="48" t="s">
-        <x:v>21</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="E10" s="44">
         <x:v>1</x:v>
@@ -924,16 +912,16 @@
     </x:row>
     <x:row r="11" ht="15" hidden="0" customHeight="1">
       <x:c r="A11" s="43" t="s">
-        <x:v>22</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="B11" s="44" t="s">
-        <x:v>12</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C11" s="44" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="D11" s="48" t="s">
-        <x:v>23</x:v>
+      <x:c r="D11" s="48" t="str">
+        <x:v>VOID FRACTION OF THE CHANNEL = VOID AREA / TOTAL AREA OF THE CHANNEL</x:v>
       </x:c>
       <x:c r="E11" s="44">
         <x:v>1</x:v>
@@ -944,16 +932,16 @@
     </x:row>
     <x:row r="12" ht="15" hidden="0" customHeight="1">
       <x:c r="A12" s="43" t="s">
-        <x:v>24</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B12" s="44" t="s">
-        <x:v>12</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C12" s="44" t="s">
-        <x:v>25</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="D12" s="48" t="s">
-        <x:v>26</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="E12" s="44">
         <x:v>-99</x:v>
@@ -964,16 +952,16 @@
     </x:row>
     <x:row r="13" ht="15" hidden="0" customHeight="1">
       <x:c r="A13" s="43" t="s">
-        <x:v>27</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B13" s="44" t="s">
-        <x:v>12</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C13" s="44" t="s">
         <x:v>4</x:v>
       </x:c>
       <x:c r="D13" s="48" t="s">
-        <x:v>28</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="E13" s="44">
         <x:v>0.02</x:v>
@@ -984,13 +972,13 @@
     </x:row>
     <x:row r="14" ht="15" hidden="0" customHeight="1">
       <x:c r="A14" s="43" t="s">
-        <x:v>29</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B14" s="44" t="s">
-        <x:v>12</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C14" s="44" t="s">
-        <x:v>30</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D14" s="48"/>
       <x:c r="E14" s="44" t="b">
@@ -1004,7 +992,7 @@
     </x:row>
     <x:row r="15" ht="15" hidden="0" customHeight="1">
       <x:c r="A15" s="43" t="s">
-        <x:v>31</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="B15" s="44" t="s">
         <x:v>7</x:v>
@@ -1022,7 +1010,7 @@
     </x:row>
     <x:row r="16" ht="15" hidden="0" customHeight="1">
       <x:c r="A16" s="43" t="s">
-        <x:v>32</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B16" s="44" t="s">
         <x:v>7</x:v>
@@ -1040,36 +1028,36 @@
     </x:row>
     <x:row r="17" ht="15" hidden="0" customHeight="1">
       <x:c r="A17" s="43" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="B17" s="44" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="C17" s="44" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="D17" s="48" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="E17" s="44" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="F17" s="44" t="s">
         <x:v>33</x:v>
-      </x:c>
-      <x:c r="B17" s="44" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="C17" s="44" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="D17" s="48" t="s">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="E17" s="44" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="F17" s="44" t="s">
-        <x:v>36</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="15" hidden="0" customHeight="1">
       <x:c r="A18" s="43" t="s">
-        <x:v>37</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="B18" s="44" t="s">
-        <x:v>12</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C18" s="44" t="s">
-        <x:v>25</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="D18" s="48" t="s">
-        <x:v>38</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="E18" s="44">
         <x:v>1</x:v>
@@ -1080,16 +1068,16 @@
     </x:row>
     <x:row r="19" ht="24" hidden="0" customHeight="1">
       <x:c r="A19" s="43" t="s">
-        <x:v>39</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="B19" s="44" t="s">
-        <x:v>12</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C19" s="44" t="s">
-        <x:v>30</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D19" s="48" t="s">
-        <x:v>40</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="E19" s="44" t="b">
         <x:v>0</x:v>
@@ -1125,7 +1113,7 @@
       </x:c>
       <x:c r="C1" s="41"/>
       <x:c r="D1" s="47" t="s">
-        <x:v>41</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="E1" s="41" t="n">
         <x:v>0</x:v>
@@ -1136,7 +1124,7 @@
       <x:c r="B2" s="34"/>
       <x:c r="C2" s="34"/>
       <x:c r="D2" s="36" t="s">
-        <x:v>42</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="E2" s="32" t="n">
         <x:f>IF(E$1&gt;0,1,0)</x:f>
@@ -1630,7 +1618,7 @@
       </x:c>
       <x:c r="C1" s="41"/>
       <x:c r="D1" s="47" t="s">
-        <x:v>43</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E1" s="41" t="n">
         <x:v>1</x:v>
@@ -1640,8 +1628,8 @@
       <x:c r="A2" s="35"/>
       <x:c r="B2" s="34"/>
       <x:c r="C2" s="34"/>
-      <x:c r="D2" s="36" t="s">
-        <x:v>44</x:v>
+      <x:c r="D2" s="36" t="str">
+        <x:v>Row used to determine the number of mixed copper-superconductor strand objects in cell B1, calculated as the sum of the values in this row starting from cell D2.</x:v>
       </x:c>
       <x:c r="E2" s="32" t="n">
         <x:f>IF(E$1&gt;0,1,0)</x:f>
@@ -2053,7 +2041,7 @@
       </x:c>
       <x:c r="C1" s="41"/>
       <x:c r="D1" s="47" t="s">
-        <x:v>45</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="E1" s="41" t="n">
         <x:v>0</x:v>
@@ -2064,7 +2052,7 @@
       <x:c r="B2" s="34"/>
       <x:c r="C2" s="34"/>
       <x:c r="D2" s="36" t="s">
-        <x:v>46</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="E2" s="32" t="n">
         <x:f>IF(E$1&gt;0,1,0)</x:f>
@@ -2117,7 +2105,7 @@
         <x:v>float</x:v>
       </x:c>
       <x:c r="D5" s="48" t="str">
-        <x:v>x coordinate of the barycenter. Not used if flag ITYMESH = -1 in file conductor_grid.</x:v>
+        <x:v>x coordinate of the barycenter. Not used if flag ITYMSH = -1 in file conductor_grid.</x:v>
       </x:c>
       <x:c r="E5" s="45" t="n">
         <x:v>0</x:v>
@@ -2134,7 +2122,7 @@
         <x:v>float</x:v>
       </x:c>
       <x:c r="D6" s="48" t="str">
-        <x:v>y coordinate of the barycenter. Not used if flag ITYMESH = -1 in file conductor_grid.</x:v>
+        <x:v>y coordinate of the barycenter. Not used if flag ITYMSH = -1 in file conductor_grid.</x:v>
       </x:c>
       <x:c r="E6" s="45" t="n">
         <x:v>0</x:v>
@@ -2235,7 +2223,7 @@
       </x:c>
       <x:c r="C1" s="41"/>
       <x:c r="D1" s="47" t="s">
-        <x:v>47</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="E1" s="41" t="n">
         <x:v>1</x:v>
@@ -2246,7 +2234,7 @@
       <x:c r="B2" s="34"/>
       <x:c r="C2" s="34"/>
       <x:c r="D2" s="36" t="s">
-        <x:v>48</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="E2" s="32" t="n">
         <x:f>IF(E$1&gt;0,1,0)</x:f>
@@ -2316,7 +2304,7 @@
         <x:v>float</x:v>
       </x:c>
       <x:c r="D6" s="48" t="str">
-        <x:v>x coordinate of the barycenter. Not used if flag ITYMESH = -1 in file conductor_grid.</x:v>
+        <x:v>x coordinate of the barycenter. Not used if flag ITYMSH = -1 in file conductor_grid.</x:v>
       </x:c>
       <x:c r="E6" s="45" t="n">
         <x:v>0</x:v>
@@ -2333,7 +2321,7 @@
         <x:v>float</x:v>
       </x:c>
       <x:c r="D7" s="48" t="str">
-        <x:v>y coordinate of the barycenter Not used if flag ITYMESH = -1 in file conductor_grid.</x:v>
+        <x:v>y coordinate of the barycenter. Not used if flag ITYMSH = -1 in file conductor_grid.</x:v>
       </x:c>
       <x:c r="E7" s="45" t="n">
         <x:v>0</x:v>
